--- a/events/Paris_2024_PG/Paris_2024_PG_Results.xlsx
+++ b/events/Paris_2024_PG/Paris_2024_PG_Results.xlsx
@@ -742,6 +742,11 @@
           <t>+3.30</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>75746</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -807,6 +812,11 @@
           <t>+9.01</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>46824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3141,6 +3151,11 @@
           <t>+3.40</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>130427</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3826,6 +3841,11 @@
           <t>42.34</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>80351</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6311,6 +6331,11 @@
           <t>+5.86</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>71726</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8721,6 +8746,11 @@
           <t>+5.67</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>46824</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8991,6 +9021,11 @@
           <t>+8.59</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>75746</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11471,6 +11506,11 @@
           <t>+1.71</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>130427</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12105,6 +12145,11 @@
           <t>+6.74</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>75746</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14091,6 +14136,11 @@
           <t>+0.85</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>80351</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15228,6 +15278,11 @@
           <t>+8.29</t>
         </is>
       </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>130427</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -17065,6 +17120,11 @@
       <c r="Q240" t="inlineStr">
         <is>
           <t>+3.59</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>71726</t>
         </is>
       </c>
     </row>
@@ -22217,7 +22277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24288,6 +24348,116 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>46824</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CASTANO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>71726</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Higinio</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>RIVERO</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>75746</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Esteban</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FARIAS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>80351</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Juan Antonio</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>VALLE</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>130427</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>KUKLA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Paris_2024_PG/Paris_2024_PG_Results.xlsx
+++ b/events/Paris_2024_PG/Paris_2024_PG_Results.xlsx
@@ -6606,6 +6606,11 @@
           <t>+1.40</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>98111</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -16917,6 +16922,11 @@
           <t>52.69</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>98111</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -20206,6 +20216,11 @@
       <c r="Q284" t="inlineStr">
         <is>
           <t>+1.34</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>98111</t>
         </is>
       </c>
     </row>
@@ -22277,7 +22292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24458,6 +24473,28 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>98111</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Steven</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>HAXTON</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Paris_2024_PG/Paris_2024_PG_Results.xlsx
+++ b/events/Paris_2024_PG/Paris_2024_PG_Results.xlsx
@@ -24481,7 +24481,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
